--- a/output/morelli-ru/changes.xlsx
+++ b/output/morelli-ru/changes.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -467,84 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>новое</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ручка дверная FIORD S5 CAFFE раздельная на квадратной розетке</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>кофе, ЦАМ</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>9012306</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>6370</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>новое</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ручка дверная FIORD S5 CRO раздельная на квадратной розетке</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>хром, ЦАМ</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>9012307</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>6960</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>новое</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ручка дверная FIORD S5 CSA раздельная на квадратной розетке</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>матовый хром, ЦАМ</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>9012305</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>6370</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
